--- a/Deliverables/BOM/Altium-Generated-BOM.xlsx
+++ b/Deliverables/BOM/Altium-Generated-BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25028"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Melih-SoundSensor\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12B59E3A-AE45-4B3F-9448-27E2A5C28377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A6735E9-12F4-460E-8CBD-5C6C172A1D14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16140" yWindow="4140" windowWidth="21600" windowHeight="11385" xr2:uid="{DDB7BBCD-CBBD-4808-9C8E-3D71A6D9844D}"/>
+    <workbookView xWindow="12780" yWindow="3945" windowWidth="21600" windowHeight="11385" xr2:uid="{46B81A19-CBF2-4BF8-BE8E-2DF85A140A99}"/>
   </bookViews>
   <sheets>
     <sheet name="Altium-Generated-BOM" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="133">
   <si>
     <t>Comment</t>
   </si>
@@ -89,7 +89,7 @@
     <t>CAP CER 1UF 25V X5R 0603</t>
   </si>
   <si>
-    <t>C3, C5, C7, C9, C11, C13, C15, C17, C20, C27, C29, C53, C55, C70, C72</t>
+    <t>C3, C5, C7, C9, C11, C13, C15, C17, C27, C29, C53, C55, C70, C72, C76, C78, C85, C#1, C#2</t>
   </si>
   <si>
     <t>CC0603KRX5R8BB105</t>
@@ -104,19 +104,31 @@
     <t>C4, C6, C8, C10, C12, C14, C16, C18</t>
   </si>
   <si>
-    <t>Cap0402</t>
+    <t>Cap 0402</t>
   </si>
   <si>
     <t>CC0402JRNPO9BN221</t>
   </si>
   <si>
+    <t>22PF</t>
+  </si>
+  <si>
+    <t>CAP CER 22PF 50V C0G/NP0 0402</t>
+  </si>
+  <si>
+    <t>C19, C20</t>
+  </si>
+  <si>
+    <t>04025A220FAT2A</t>
+  </si>
+  <si>
     <t>0.1uF</t>
   </si>
   <si>
     <t>CAP CER 0.1UF 100V X7R 0603</t>
   </si>
   <si>
-    <t>C19, C21, C22, C23, C24, C25, C26, C28, C30, C31, C32, C33, C34, C35, C37, C38, C39, C40, C41, C42, C54, C58, C59, C71</t>
+    <t>C21, C22, C23, C24, C25, C26, C28, C30, C31, C32, C33, C34, C35, C37, C38, C39, C40, C41, C42, C54, C58, C59, C71, C77, C79, C81, C82, C84</t>
   </si>
   <si>
     <t>CC0603KRX7R0BB104</t>
@@ -158,6 +170,45 @@
     <t>CC0603KRX7R8BB684</t>
   </si>
   <si>
+    <t>10uF'</t>
+  </si>
+  <si>
+    <t>C75</t>
+  </si>
+  <si>
+    <t>100pF</t>
+  </si>
+  <si>
+    <t>CAP CER 100PF 25V X7R 0603</t>
+  </si>
+  <si>
+    <t>C80</t>
+  </si>
+  <si>
+    <t>CC0603KRX7R8BB101</t>
+  </si>
+  <si>
+    <t>3.3nF</t>
+  </si>
+  <si>
+    <t>CAP CER 3300PF 50V X7R 0402</t>
+  </si>
+  <si>
+    <t>C83</t>
+  </si>
+  <si>
+    <t>CGA2B2X7R1H332M050BA</t>
+  </si>
+  <si>
+    <t>UDD32C03L01</t>
+  </si>
+  <si>
+    <t>15V 19A 3.3V 4V Bidirectional SOD-323 ESD Protection Devices ROHS</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
     <t>3-644456-5</t>
   </si>
   <si>
@@ -167,10 +218,13 @@
     <t>J1</t>
   </si>
   <si>
-    <t>DC-0920-SMT</t>
-  </si>
-  <si>
-    <t>Surface Mount DC Power Receptacle 1.2mm 3.7mm SMD AC/DC Power Connectors ROHS</t>
+    <t>HDR1X5</t>
+  </si>
+  <si>
+    <t>10118194-0001LF</t>
+  </si>
+  <si>
+    <t>CONN RCPT USB2.0 MICRO B SMD R/A</t>
   </si>
   <si>
     <t>J2</t>
@@ -188,6 +242,21 @@
     <t>2 Pin JST Connector</t>
   </si>
   <si>
+    <t>2nH</t>
+  </si>
+  <si>
+    <t>2nH ±0.3nH 0603 Inductors</t>
+  </si>
+  <si>
+    <t>L1</t>
+  </si>
+  <si>
+    <t>IND 0603</t>
+  </si>
+  <si>
+    <t>SDCL1608C2N0STDF</t>
+  </si>
+  <si>
     <t>ICS-40730</t>
   </si>
   <si>
@@ -203,7 +272,7 @@
     <t>RES SMD 100K OHM 5% 1/5W 0603</t>
   </si>
   <si>
-    <t>R1, R2</t>
+    <t>R1, R2, R3</t>
   </si>
   <si>
     <t>Res0603</t>
@@ -212,6 +281,30 @@
     <t>CRGH0603J100K</t>
   </si>
   <si>
+    <t>499K</t>
+  </si>
+  <si>
+    <t>RES SMD 499K OHM 1% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>R4</t>
+  </si>
+  <si>
+    <t>AC0603FR-07499KL</t>
+  </si>
+  <si>
+    <t>20K</t>
+  </si>
+  <si>
+    <t>RES SMD 20K OHM 1% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>R5</t>
+  </si>
+  <si>
+    <t>RC0603FR-0720KL</t>
+  </si>
+  <si>
     <t>10K</t>
   </si>
   <si>
@@ -230,7 +323,7 @@
     <t>Solder Bridge ON</t>
   </si>
   <si>
-    <t>SB1, SB2, SB3, SB8, SB9, SB10, SB11, SB12, SB13, SB14, SB15, SB16, SB17, SB18, SB19, SB20, SB21, SB22, SB23, SB24, SB25, SB26, SB27, SB28, SB29, SB30, SB32, SB34, SB35, SB36, SB37, SB38, SB40, SB41, SB42, SB44, SB45, SB46, SB47, SB48, SB49, SB50</t>
+    <t>SB1, SB2, SB3, SB4, SB5, SB8, SB9, SB10, SB11, SB12, SB13, SB14, SB15, SB16, SB17, SB18, SB19, SB20, SB21, SB22, SB23, SB24, SB25, SB26, SB27, SB28, SB29, SB30, SB32, SB34, SB35, SB36, SB37, SB38, SB40, SB41, SB42, SB44, SB45, SB46, SB47, SB48, SB49, SB50, SB70, SB71, SB72</t>
   </si>
   <si>
     <t>TS-1185EC-C-D-B</t>
@@ -287,13 +380,25 @@
     <t>U5, U6</t>
   </si>
   <si>
-    <t>ESP32-WROOM-32E(8MB)</t>
-  </si>
-  <si>
-    <t>Rx Txrx Mod Wifi Trace Ant SMD</t>
-  </si>
-  <si>
-    <t>U12</t>
+    <t>ESP32-D0WD-V3</t>
+  </si>
+  <si>
+    <t>IC RF TXRX+MCU BLUETOOTH WIFI</t>
+  </si>
+  <si>
+    <t>U7</t>
+  </si>
+  <si>
+    <t>MX25L8006EM2I-12G</t>
+  </si>
+  <si>
+    <t>IC FLASH 8MBIT SPI 86MHZ 8SOP</t>
+  </si>
+  <si>
+    <t>U8</t>
+  </si>
+  <si>
+    <t>SOP-8</t>
   </si>
   <si>
     <t>UMH3N</t>
@@ -321,6 +426,15 @@
   </si>
   <si>
     <t>X2, X3</t>
+  </si>
+  <si>
+    <t>X322540MPB4SI</t>
+  </si>
+  <si>
+    <t>40MHz SMD Crystal Resonator 15pF ±10ppm ±30ppm -40℃~+85℃ SMD3225-4P Crystals ROHS</t>
+  </si>
+  <si>
+    <t>X4</t>
   </si>
 </sst>
 </file>
@@ -383,12 +497,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -702,511 +819,711 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56EE264A-2F57-4604-A2EC-8AE793C83E92}">
-  <dimension ref="A1:F25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC0CFCAF-505C-419D-A64D-44D3499BF423}">
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="6" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="1">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="4">
-        <v>15</v>
+      <c r="F4" s="1">
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="1">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="4">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="E7" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="5">
         <v>28</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="3" t="s">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F8" s="4">
+      <c r="E9" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="5">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="3" t="s">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="4">
+      <c r="E10" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="5">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F10" s="4">
-        <v>1</v>
-      </c>
-    </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B11" s="3" t="s">
+      <c r="A11" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="B11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F11" s="4">
+      <c r="D11" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E12" s="3" t="s">
+      <c r="D12" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F13" s="4">
+      <c r="D13" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F14" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F15" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F16" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F17" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F18" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F19" s="5">
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F14" s="4">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F20" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F21" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="F22" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F23" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F24" s="5">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F25" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F26" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="F15" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F16" s="4">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F17" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F18" s="4">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="F27" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="F28" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="F29" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F19" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="F20" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F21" s="4">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="F30" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F31" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="F32" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="F33" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="F34" s="7">
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="F22" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F23" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="F24" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F25" s="4">
-        <v>2</v>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="F35" s="7">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Deliverables/BOM/Altium-Generated-BOM.xlsx
+++ b/Deliverables/BOM/Altium-Generated-BOM.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Melih-SoundSensor\Deliverables\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark\Melih-SoundSensor\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12B59E3A-AE45-4B3F-9448-27E2A5C28377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16140" yWindow="4140" windowWidth="21600" windowHeight="11385" xr2:uid="{DDB7BBCD-CBBD-4808-9C8E-3D71A6D9844D}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="6705"/>
   </bookViews>
   <sheets>
     <sheet name="Altium-Generated-BOM" sheetId="1" r:id="rId1"/>
@@ -18,25 +17,17 @@
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Altium-Generated-BOM'!$1:$1</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="109">
   <si>
     <t>Comment</t>
   </si>
@@ -56,6 +47,9 @@
     <t>Quantity</t>
   </si>
   <si>
+    <t>Manufacturer</t>
+  </si>
+  <si>
     <t>10uF</t>
   </si>
   <si>
@@ -71,6 +65,9 @@
     <t>CL10A106MA8NRNC</t>
   </si>
   <si>
+    <t>Samsung</t>
+  </si>
+  <si>
     <t>4.7UF</t>
   </si>
   <si>
@@ -89,12 +86,15 @@
     <t>CAP CER 1UF 25V X5R 0603</t>
   </si>
   <si>
-    <t>C3, C5, C7, C9, C11, C13, C15, C17, C20, C27, C29, C53, C55, C70, C72</t>
+    <t>C3, C5, C7, C9, C11, C13, C15, C17, C20, C27, C29, C53, C55, C70, C72, C#1, C#2</t>
   </si>
   <si>
     <t>CC0603KRX5R8BB105</t>
   </si>
   <si>
+    <t>Yageo</t>
+  </si>
+  <si>
     <t>220pF</t>
   </si>
   <si>
@@ -104,7 +104,7 @@
     <t>C4, C6, C8, C10, C12, C14, C16, C18</t>
   </si>
   <si>
-    <t>Cap0402</t>
+    <t>Cap 0402</t>
   </si>
   <si>
     <t>CC0402JRNPO9BN221</t>
@@ -134,6 +134,9 @@
     <t>UMK107C7224KAHTE</t>
   </si>
   <si>
+    <t>Taiyo Yuden</t>
+  </si>
+  <si>
     <t>18pF</t>
   </si>
   <si>
@@ -167,15 +170,24 @@
     <t>J1</t>
   </si>
   <si>
-    <t>DC-0920-SMT</t>
-  </si>
-  <si>
-    <t>Surface Mount DC Power Receptacle 1.2mm 3.7mm SMD AC/DC Power Connectors ROHS</t>
+    <t>HDR1X5</t>
+  </si>
+  <si>
+    <t>TE Connectivity</t>
+  </si>
+  <si>
+    <t>10118194-0001LF</t>
+  </si>
+  <si>
+    <t>CONN RCPT USB2.0 MICRO B SMD R/A</t>
   </si>
   <si>
     <t>J2</t>
   </si>
   <si>
+    <t>Amphenol FCI</t>
+  </si>
+  <si>
     <t>JST Connector</t>
   </si>
   <si>
@@ -197,13 +209,16 @@
     <t>MK1, MK2, MK3, MK4, MK5, MK6, MK7, MK8</t>
   </si>
   <si>
+    <t>TDK InvenSense</t>
+  </si>
+  <si>
     <t>100K</t>
   </si>
   <si>
     <t>RES SMD 100K OHM 5% 1/5W 0603</t>
   </si>
   <si>
-    <t>R1, R2</t>
+    <t>R1, R2, R3</t>
   </si>
   <si>
     <t>Res0603</t>
@@ -230,7 +245,7 @@
     <t>Solder Bridge ON</t>
   </si>
   <si>
-    <t>SB1, SB2, SB3, SB8, SB9, SB10, SB11, SB12, SB13, SB14, SB15, SB16, SB17, SB18, SB19, SB20, SB21, SB22, SB23, SB24, SB25, SB26, SB27, SB28, SB29, SB30, SB32, SB34, SB35, SB36, SB37, SB38, SB40, SB41, SB42, SB44, SB45, SB46, SB47, SB48, SB49, SB50</t>
+    <t>SB1, SB2, SB3, SB4, SB5, SB8, SB9, SB10, SB11, SB12, SB13, SB14, SB15, SB16, SB17, SB18, SB19, SB20, SB21, SB22, SB23, SB24, SB25, SB26, SB27, SB28, SB29, SB30, SB32, SB34, SB35, SB36, SB37, SB38, SB40, SB41, SB42, SB44, SB45, SB46, SB47, SB48, SB49, SB50, SB70, SB71, SB72</t>
   </si>
   <si>
     <t>TS-1185EC-C-D-B</t>
@@ -242,6 +257,9 @@
     <t>SW1</t>
   </si>
   <si>
+    <t>XKB</t>
+  </si>
+  <si>
     <t>LM66100DCKR</t>
   </si>
   <si>
@@ -254,6 +272,9 @@
     <t>SC70-6</t>
   </si>
   <si>
+    <t>Texas Instruments</t>
+  </si>
+  <si>
     <t>XC6220B331MR-G</t>
   </si>
   <si>
@@ -266,6 +287,9 @@
     <t>SOT-25</t>
   </si>
   <si>
+    <t>Torex</t>
+  </si>
+  <si>
     <t>ADS131M08IPBSR</t>
   </si>
   <si>
@@ -296,6 +320,9 @@
     <t>U12</t>
   </si>
   <si>
+    <t>Espressif Systems</t>
+  </si>
+  <si>
     <t>UMH3N</t>
   </si>
   <si>
@@ -305,6 +332,9 @@
     <t>U13</t>
   </si>
   <si>
+    <t>Changjiang</t>
+  </si>
+  <si>
     <t>3TJ481920NYLBC</t>
   </si>
   <si>
@@ -312,6 +342,9 @@
   </si>
   <si>
     <t>X1</t>
+  </si>
+  <si>
+    <t>JYJE</t>
   </si>
   <si>
     <t>S3224576121060</t>
@@ -326,7 +359,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -336,7 +369,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -346,12 +379,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD3D3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -385,10 +412,10 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -423,7 +450,7 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
         <a:srgbClr val="ED7D31"/>
@@ -435,7 +462,7 @@
         <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
         <a:srgbClr val="70AD47"/>
@@ -482,23 +509,6 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -534,23 +544,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -702,512 +695,582 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56EE264A-2F57-4604-A2EC-8AE793C83E92}">
-  <dimension ref="A1:F25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="6" width="19.7109375" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="4">
+      <c r="E2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="4">
+      <c r="C3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="G3" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="1">
+        <v>17</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="1">
+        <v>8</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="1">
+        <v>24</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="1">
+        <v>6</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" s="1">
         <v>16</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="4">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="G9" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="4">
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" s="1">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="4">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" s="4">
+      <c r="G13" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F14" s="1">
+        <v>3</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F15" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F8" s="4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="4">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F10" s="4">
+      <c r="G15" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F16" s="1">
+        <v>47</v>
+      </c>
+      <c r="G16" s="1"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F17" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F11" s="4">
+      <c r="G17" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F18" s="1">
+        <v>2</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F19" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F12" s="4">
+      <c r="G19" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F20" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F13" s="4">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F14" s="4">
+      <c r="G20" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F21" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="F15" s="4">
+      <c r="G21" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F22" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F16" s="4">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F17" s="4">
+      <c r="G22" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F23" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F18" s="4">
+      <c r="G23" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F24" s="1">
+        <v>1</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F25" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F19" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="F20" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F21" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="F22" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F23" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="F24" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F25" s="4">
-        <v>2</v>
-      </c>
+      <c r="G25" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Deliverables/BOM/Altium-Generated-BOM.xlsx
+++ b/Deliverables/BOM/Altium-Generated-BOM.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25028"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Melih-SoundSensor\Deliverables\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark\Melih-SoundSensor\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A6735E9-12F4-460E-8CBD-5C6C172A1D14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12780" yWindow="3945" windowWidth="21600" windowHeight="11385" xr2:uid="{46B81A19-CBF2-4BF8-BE8E-2DF85A140A99}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="6705"/>
   </bookViews>
   <sheets>
     <sheet name="Altium-Generated-BOM" sheetId="1" r:id="rId1"/>
@@ -18,25 +17,17 @@
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Altium-Generated-BOM'!$1:$1</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="212">
   <si>
     <t>Comment</t>
   </si>
@@ -56,6 +47,9 @@
     <t>Quantity</t>
   </si>
   <si>
+    <t>Manufacturer</t>
+  </si>
+  <si>
     <t>10uF</t>
   </si>
   <si>
@@ -71,6 +65,9 @@
     <t>CL10A106MA8NRNC</t>
   </si>
   <si>
+    <t>Samsung</t>
+  </si>
+  <si>
     <t>4.7UF</t>
   </si>
   <si>
@@ -95,6 +92,9 @@
     <t>CC0603KRX5R8BB105</t>
   </si>
   <si>
+    <t>Yageo</t>
+  </si>
+  <si>
     <t>220pF</t>
   </si>
   <si>
@@ -122,6 +122,9 @@
     <t>04025A220FAT2A</t>
   </si>
   <si>
+    <t>Kyocera AVX</t>
+  </si>
+  <si>
     <t>0.1uF</t>
   </si>
   <si>
@@ -146,6 +149,9 @@
     <t>UMK107C7224KAHTE</t>
   </si>
   <si>
+    <t>Taiyo Yuden</t>
+  </si>
+  <si>
     <t>18pF</t>
   </si>
   <si>
@@ -200,6 +206,69 @@
     <t>CGA2B2X7R1H332M050BA</t>
   </si>
   <si>
+    <t>TDK</t>
+  </si>
+  <si>
+    <t>4.7nF</t>
+  </si>
+  <si>
+    <t>CAP SMD 4700pF ±10% 25V X7R 0603</t>
+  </si>
+  <si>
+    <t>C86</t>
+  </si>
+  <si>
+    <t>CC0603KRX7R8BB472</t>
+  </si>
+  <si>
+    <t>CAP CER 0.1UF 50V X7R 0402</t>
+  </si>
+  <si>
+    <t>C87</t>
+  </si>
+  <si>
+    <t>GRM155R71H104ME14D</t>
+  </si>
+  <si>
+    <t>Murata</t>
+  </si>
+  <si>
+    <t>33nF</t>
+  </si>
+  <si>
+    <t>CAP CER 33000pF ±10% 25V X7R 0603</t>
+  </si>
+  <si>
+    <t>C88, C89</t>
+  </si>
+  <si>
+    <t>CC0603KRX7R8BB333</t>
+  </si>
+  <si>
+    <t>2.7pF</t>
+  </si>
+  <si>
+    <t>CAP SMD  2.7pF ±0.25pF 50V NPO 0603</t>
+  </si>
+  <si>
+    <t>C90</t>
+  </si>
+  <si>
+    <t>CC0603CRNPO9BN2R7</t>
+  </si>
+  <si>
+    <t>4.7pF</t>
+  </si>
+  <si>
+    <t>CAP SMD 4.7pF ±0.1pF 50V NPO 0603</t>
+  </si>
+  <si>
+    <t>C91</t>
+  </si>
+  <si>
+    <t>CC0603BRNPO9BN4R7</t>
+  </si>
+  <si>
     <t>UDD32C03L01</t>
   </si>
   <si>
@@ -209,6 +278,24 @@
     <t>D1</t>
   </si>
   <si>
+    <t>Brightking</t>
+  </si>
+  <si>
+    <t>TPD1E10B06DPYR</t>
+  </si>
+  <si>
+    <t>DIODE TVS SMD 5.5V 5A 90W</t>
+  </si>
+  <si>
+    <t>D2, D3</t>
+  </si>
+  <si>
+    <t>X1SON - 0.45 mm max height</t>
+  </si>
+  <si>
+    <t>Texas Instruments</t>
+  </si>
+  <si>
     <t>3-644456-5</t>
   </si>
   <si>
@@ -221,15 +308,21 @@
     <t>HDR1X5</t>
   </si>
   <si>
-    <t>10118194-0001LF</t>
-  </si>
-  <si>
-    <t>CONN RCPT USB2.0 MICRO B SMD R/A</t>
+    <t>TE Connectivity</t>
+  </si>
+  <si>
+    <t>U262-061N-4BVC11</t>
+  </si>
+  <si>
+    <t>USB 3.1 1 Surface Mount 6 Female -25℃~+85℃ Type-C SMD USB Connectors ROHS</t>
   </si>
   <si>
     <t>J2</t>
   </si>
   <si>
+    <t>XKB</t>
+  </si>
+  <si>
     <t>JST Connector</t>
   </si>
   <si>
@@ -242,6 +335,18 @@
     <t>2 Pin JST Connector</t>
   </si>
   <si>
+    <t>U.FL-R-SMT-1(80)</t>
+  </si>
+  <si>
+    <t>CONN U.FL RCPT STR 50 OHM SMD</t>
+  </si>
+  <si>
+    <t>J4</t>
+  </si>
+  <si>
+    <t>Hirose</t>
+  </si>
+  <si>
     <t>2nH</t>
   </si>
   <si>
@@ -257,6 +362,48 @@
     <t>SDCL1608C2N0STDF</t>
   </si>
   <si>
+    <t>Sunlord</t>
+  </si>
+  <si>
+    <t>3.3nH</t>
+  </si>
+  <si>
+    <t>FIXED IND 3.3NH 1A 120 MOHM SMD</t>
+  </si>
+  <si>
+    <t>L2, L3</t>
+  </si>
+  <si>
+    <t>LQG18HN3N3S00D</t>
+  </si>
+  <si>
+    <t>1.2nH</t>
+  </si>
+  <si>
+    <t>FIXED IND 1.2NH 1A 90 MOHM SMD</t>
+  </si>
+  <si>
+    <t>L4, L5</t>
+  </si>
+  <si>
+    <t>IND 0402</t>
+  </si>
+  <si>
+    <t>LQG15HS1N2S02D</t>
+  </si>
+  <si>
+    <t>1.6nH</t>
+  </si>
+  <si>
+    <t>IND 700mA 1.6nH ±10% 40mΩ 0603</t>
+  </si>
+  <si>
+    <t>L6</t>
+  </si>
+  <si>
+    <t>FHW0603UC1N6KST</t>
+  </si>
+  <si>
     <t>ICS-40730</t>
   </si>
   <si>
@@ -266,6 +413,27 @@
     <t>MK1, MK2, MK3, MK4, MK5, MK6, MK7, MK8</t>
   </si>
   <si>
+    <t>TDK InvenSense</t>
+  </si>
+  <si>
+    <t>61300611121</t>
+  </si>
+  <si>
+    <t>CONN HEADER VERT 6POS 2.54MM</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>HDR1X6</t>
+  </si>
+  <si>
+    <t>e-50004</t>
+  </si>
+  <si>
+    <t>Wurth Electronics</t>
+  </si>
+  <si>
     <t>100K</t>
   </si>
   <si>
@@ -281,16 +449,16 @@
     <t>CRGH0603J100K</t>
   </si>
   <si>
-    <t>499K</t>
-  </si>
-  <si>
-    <t>RES SMD 499K OHM 1% 1/10W 0603</t>
+    <t>499R</t>
+  </si>
+  <si>
+    <t>RES SMD 499Ω ± 1.00% 0.1W ± 100ppm/℃ 0603</t>
   </si>
   <si>
     <t>R4</t>
   </si>
   <si>
-    <t>AC0603FR-07499KL</t>
+    <t>RC0603FR-07499RL</t>
   </si>
   <si>
     <t>20K</t>
@@ -305,13 +473,25 @@
     <t>RC0603FR-0720KL</t>
   </si>
   <si>
+    <t>0R</t>
+  </si>
+  <si>
+    <t>RES SMD 0R, 1%, 0.1W, 0603</t>
+  </si>
+  <si>
+    <t>R6, R7, R8, R9</t>
+  </si>
+  <si>
+    <t>RC0603FR-070RL</t>
+  </si>
+  <si>
     <t>10K</t>
   </si>
   <si>
     <t>RES SMD 10K OHM 1% 1/10W 0603</t>
   </si>
   <si>
-    <t>R17</t>
+    <t>R10, R17</t>
   </si>
   <si>
     <t>RC0603FR-0710KL</t>
@@ -323,7 +503,7 @@
     <t>Solder Bridge ON</t>
   </si>
   <si>
-    <t>SB1, SB2, SB3, SB4, SB5, SB8, SB9, SB10, SB11, SB12, SB13, SB14, SB15, SB16, SB17, SB18, SB19, SB20, SB21, SB22, SB23, SB24, SB25, SB26, SB27, SB28, SB29, SB30, SB32, SB34, SB35, SB36, SB37, SB38, SB40, SB41, SB42, SB44, SB45, SB46, SB47, SB48, SB49, SB50, SB70, SB71, SB72</t>
+    <t>SB1, SB2, SB3, SB4, SB5, SB6, SB7, SB8, SB9, SB10, SB11, SB12, SB13, SB14, SB15, SB16, SB17, SB18, SB19, SB20, SB21, SB22, SB23, SB24, SB25, SB26, SB27, SB28, SB29, SB30, SB31, SB32, SB33, SB34, SB35, SB36, SB37, SB38, SB39, SB40, SB41, SB42, SB43, SB44, SB45, SB46, SB47, SB48, SB49, SB50, SB51, SB52, SB70, SB71, SB72</t>
   </si>
   <si>
     <t>TS-1185EC-C-D-B</t>
@@ -359,6 +539,9 @@
     <t>SOT-25</t>
   </si>
   <si>
+    <t>Torex</t>
+  </si>
+  <si>
     <t>ADS131M08IPBSR</t>
   </si>
   <si>
@@ -389,6 +572,9 @@
     <t>U7</t>
   </si>
   <si>
+    <t>Espressif Systems</t>
+  </si>
+  <si>
     <t>MX25L8006EM2I-12G</t>
   </si>
   <si>
@@ -401,6 +587,39 @@
     <t>SOP-8</t>
   </si>
   <si>
+    <t>Macronix</t>
+  </si>
+  <si>
+    <t>PRO-OB-440</t>
+  </si>
+  <si>
+    <t>RF ANT 2.4GHZ STAMPED MET SLD</t>
+  </si>
+  <si>
+    <t>U9</t>
+  </si>
+  <si>
+    <t>Proant</t>
+  </si>
+  <si>
+    <t>ESP-PSRAM64H</t>
+  </si>
+  <si>
+    <t>IC PSRAM 64MBIT SPI 133MHZ 8SOIC</t>
+  </si>
+  <si>
+    <t>U10</t>
+  </si>
+  <si>
+    <t>SOIC-8</t>
+  </si>
+  <si>
+    <t>4677</t>
+  </si>
+  <si>
+    <t>Adafruit Industries</t>
+  </si>
+  <si>
     <t>UMH3N</t>
   </si>
   <si>
@@ -410,6 +629,9 @@
     <t>U13</t>
   </si>
   <si>
+    <t>Changjiang</t>
+  </si>
+  <si>
     <t>3TJ481920NYLBC</t>
   </si>
   <si>
@@ -419,6 +641,9 @@
     <t>X1</t>
   </si>
   <si>
+    <t>JYJE</t>
+  </si>
+  <si>
     <t>S3224576121060</t>
   </si>
   <si>
@@ -435,12 +660,15 @@
   </si>
   <si>
     <t>X4</t>
+  </si>
+  <si>
+    <t>Yangxing Tech</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -450,7 +678,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -460,12 +688,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD3D3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -497,15 +719,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -540,7 +759,7 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
         <a:srgbClr val="ED7D31"/>
@@ -552,7 +771,7 @@
         <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
         <a:srgbClr val="70AD47"/>
@@ -599,23 +818,6 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -651,23 +853,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -819,711 +1004,1129 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC0CFCAF-505C-419D-A64D-44D3499BF423}">
-  <dimension ref="A1:F35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="6" width="19.7109375" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="4" t="s">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>10</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="F2" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="G2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="4" t="s">
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="C3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="F3" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="4" t="s">
+      <c r="G3" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>18</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="F4" s="1">
         <v>19</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="G4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="4" t="s">
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="B5" s="2" t="s">
         <v>23</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="F5" s="1">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="4" t="s">
+      <c r="G5" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="5">
+      <c r="E6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="G6" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="1">
         <v>28</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" s="5">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="G7" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" s="1">
+        <v>6</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="1">
+        <v>16</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F8" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F10" s="5">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="4" t="s">
+      <c r="B15" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F12" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F13" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B14" s="4" t="s">
+      <c r="E16" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F16" s="1">
+        <v>2</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F19" s="1">
+        <v>1</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F20" s="1">
+        <v>2</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F21" s="1">
+        <v>1</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F22" s="1">
+        <v>1</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F23" s="1">
+        <v>1</v>
+      </c>
+      <c r="G23" s="1"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F24" s="1">
+        <v>1</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F26" s="1">
+        <v>2</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F27" s="1">
+        <v>2</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F28" s="1">
+        <v>1</v>
+      </c>
+      <c r="G28" s="1"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F29" s="1">
+        <v>8</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F30" s="1">
+        <v>1</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F31" s="1">
+        <v>3</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F32" s="1">
+        <v>1</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F33" s="1">
+        <v>1</v>
+      </c>
+      <c r="G33" s="1"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F34" s="1">
+        <v>4</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F35" s="1">
+        <v>2</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="F36" s="1">
         <v>55</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F14" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F15" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F16" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="F17" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="F18" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="F19" s="5">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F20" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="F21" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E22" s="4" t="s">
+      <c r="G36" s="1"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F37" s="1">
+        <v>1</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="F38" s="1">
+        <v>2</v>
+      </c>
+      <c r="G38" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="F22" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F23" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="F24" s="5">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="F25" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="F26" s="5">
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="F39" s="1">
+        <v>1</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="F40" s="1">
+        <v>1</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F41" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="F27" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="F28" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="F29" s="5">
+      <c r="G41" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F42" s="1">
+        <v>1</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="F43" s="1">
+        <v>1</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F44" s="1">
+        <v>1</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="F45" s="1">
+        <v>1</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="F46" s="1">
+        <v>1</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F47" s="1">
+        <v>1</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="F48" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="F30" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="F31" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="F32" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="F33" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="F34" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="F35" s="7">
-        <v>1</v>
+      <c r="G48" s="1"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F49" s="1">
+        <v>1</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>211</v>
       </c>
     </row>
   </sheetData>
